--- a/source_docs/Ithaka-Portico-KnowledgeBase.xlsx
+++ b/source_docs/Ithaka-Portico-KnowledgeBase.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30224"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innodata-my.sharepoint.com/personal/vff_innodata_com/Documents/Shared with Everyone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="341" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8A90B196-F6B6-4511-B917-773D6A39D8E7}"/>
+  <xr:revisionPtr revIDLastSave="450" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5890746-5E04-45E4-BA60-06D5E034FCD7}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="WorkBench-Errors-Resolution" sheetId="1" r:id="rId1"/>
+    <sheet name="00_DOMAINS_AND_METADATA" sheetId="2" r:id="rId1"/>
+    <sheet name="WorkBench-Errors-Resolution" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="118">
   <si>
     <t>Developer</t>
   </si>
@@ -56,9 +57,6 @@
     <t>Knowledge Source</t>
   </si>
   <si>
-    <t>Date</t>
-  </si>
-  <si>
     <t>Jira/Email detail</t>
   </si>
   <si>
@@ -69,9 +67,6 @@
   </si>
   <si>
     <t>MICROBIO-BL-SETUP-24610</t>
-  </si>
-  <si>
-    <t>C550</t>
   </si>
   <si>
     <t>TOOL032 - Bad data: Value of 'xml:lang' attribute of element ref not equal to a RFC 3066 value (as defined by ISO 639-1 | ISO 639-2 | ISO 639-3). 
@@ -161,6 +156,9 @@
 - Final Resolution: Script Fix</t>
   </si>
   <si>
+    <t>C550</t>
+  </si>
+  <si>
     <t>TOOL001 - QCA774, Bad data: Value of 'country' attribute of element country not equal to codes defined by ISO in ISO 3166 and listed at: http://www.iso.org/iso/country_codes/iso_3166_code_lists.htm. These codes are subject to change, so if this error is raised, be sure to check the ISO web site to see if this is a genuine error, or if thePortico Schematron file must be updated to include a new value.:::/article[1]/front[1]/article-meta[1]/aff[1]/country[1]</t>
   </si>
   <si>
@@ -411,16 +409,127 @@
     <t>- Month must be present in [ pub-date ] when Year and Day are given.
 - Resolution: Script logiv FIXED template "pub-date"</t>
   </si>
+  <si>
+    <t>PORTLAND JATS E-Journals - BL-SETUP-24894</t>
+  </si>
+  <si>
+    <t>C512</t>
+  </si>
+  <si>
+    <t>C512 : SU 13 (Category: Processing) Step : PorticoWorkflow_4_3_ResolveFileReferences
+No file found for the token 'ETLS-2025-3021.pdf' referenced in the generated(target) lead MD file etls/237353/etls-2025-3021-xml/conprep_generated/tms3qc7v3nn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- Dropping Reference of PDF File for Full-Text Content.
+- Publisher confirmed that PDF file not available on Publisher's website
+- Resolution: we are dropping the reference to the PDF file from the element 'self-uri'.
+</t>
+  </si>
+  <si>
+    <t>NAPC JATS E-Journals</t>
+  </si>
+  <si>
+    <t>C550 (Category: Tool) Step : PorticoWorkflow_4_3_ReplaceFileReferences
+Automated QC detected errors in the generated(target) lead MD file ajas/ajas_5_1502/ajas-xml/conprep_generated/tms3xzm0666
+Messages Content:
+TOOL001 - QCA753, Programming exception: Element abstract should have a title and does not.:::/article[1]/front[1]/article-meta[1]/abstract[1]
+TOOL001 - QCA753, Programming exception: Element kwd-group should have a title and does not.:::/article[1]/front[1]/article-meta[1]/kwd-group[1]</t>
+  </si>
+  <si>
+    <t>- Publisher has not provided title element in the abstract and kwd-group
+- Resolution: We are genrating the title element in the output through "insert-titles-jats.xsl" script.</t>
+  </si>
+  <si>
+    <t>C550 : SU 61 (Category: Tool) Step : PorticoWorkflow_4_3_ReplaceFileReferences
+Automated QC detected errors in the generated(target) lead MD file bio/237596/bio-2026-203-xml/conprep_generated/tms3q1c6gm8</t>
+  </si>
+  <si>
+    <t>- Element graphic should have a position attribute equal to 'anchor'.
+- Resolution: We updated the transformation script to change the position attribute equal to 'anchor'.</t>
+  </si>
+  <si>
+    <t>WSPC ATY E-Journals-SETUP-25056</t>
+  </si>
+  <si>
+    <t>C500 : SU 17 (Category: Processing) Step : PorticoWorkflow_4_3_TransformFiles
+Failed to transform the supplied file ac.33.issue-02_20260512194254.zip/s1005386726000180/s1005386726000180.xml</t>
+  </si>
+  <si>
+    <t>- Unhandled Value of Attribute '@rid' and '@id'
+- Resolution: We updated the transformation script to handled the ID and RID issues.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">- A sequence of more than one item is not allowed as the first argument of fn:normalize-space()
+- Resolution: We updated the transformation script to handled these type issues.
+</t>
+  </si>
+  <si>
+    <t>C464 (Category: Processing) Step : PorticoWorkflow_4_3_TransformFiles
+Generated file ajas/ajas_5_1502/ajas-xml/conprep_generated/tms3xzp1nbh well-formed but not valid.
+Messages Content:
+TOOL014 - The file is well-formed but not valid for the format: PTC_JATS_Archiving_MML2_DTD_1.3
+SAXParseException. Attribute "content-type" must be declared for element type "ext-link". Line = 14, Column = 200.SAXParseException. The content of element type "article-meta" must match "(article-id*,(article-version|article-version-alternatives)?,article-categories?,title-group?,(contrib-group|aff|aff-alternatives|x)*,author-notes?,(pub-date*|pub-date-not-available?),volume*,volume-id*,volume-series?,issue*,issue-id*,issue-title*,issue-title-group*,issue-sponsor*,issue-part?,volume-issue-group*,isbn*,supplement?,(((fpage,lpage?)?,page-range?)|elocation-id)?,(email|ext-link|uri|product|supplementary-material)*,history?,pub-history?,permissions?,self-uri*,(related-article|related-object)*,abstract*,trans-abstract*,kwd-group*,funding-group*,support-group*,conference*,counts?,custom-meta-group?)". Line = 14, Column = 2,304.</t>
+  </si>
+  <si>
+    <t>- Attribute @content-type is not valid as per the PTC output format.
+- Resolution: We need to updating the transform script and resolved this issue.</t>
+  </si>
+  <si>
+    <t>C448 (Category: Configuration) Step : PorticoWorkflow_4_3_CheckForCompleteness
+Orphan File /pcontent/ongoing/journal_content/INGEST_MASTER/NAPC/Fetched/SELF/NEW/nap_portico_complete/ajas_5_1_2013.zip/_manifest.txt: not fully unit identified.
+Messages Content:
+Check file naming and Profile rules</t>
+  </si>
+  <si>
+    <t>- Publisher porvided the extra files in the ZIP.
+- Resolution: If we are not able to group any file in the any CU and publisher not provided reference of provided file we have checked this file and exculde such type file through FER rule.</t>
+  </si>
+  <si>
+    <t>MRE JATS E-Journals-SETUP-25050</t>
+  </si>
+  <si>
+    <t>Orphan File /pcontent/ongoing/journal_content/INGEST_MASTER/MRE/Fetched/JATS/NEW/SV/SV_18_2_2022.zip/SV_18_2_2022/SV2021050701/SV2021050701_Immediate_Effect_Supplement_1.docx: not fully unit identified.</t>
+  </si>
+  <si>
+    <t>- Supplementary files are not getting to identified by the current rule 'InterpretPackagingRuleSet'
+- Resolution: We updated the associated rule and now files are correct identified</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Orphan File /pcontent/ongoing/journal_content/INGEST_MASTER/MRE/Fetched/JATS/NEW/EJGO/EJGO_43_3_2022.zip/EJGO_43_3_2022/EJGO22012001/video1.png: not fully unit identified.
+</t>
+  </si>
+  <si>
+    <t>- Image files are not getting to identified by the current rule 'InterpretPackagingRuleSet'
+- Resolution: We updated the associated rule and now files are correct identified</t>
+  </si>
+  <si>
+    <t>C464 : SU 85 (Category: Processing) Step : PorticoWorkflow_4_3_TransformFiles
+Generated file EMERALD E-Books/978-1-59311-357-5/xml/conprep_generated/tms2gvmxdb1 well-formed but not valid.</t>
+  </si>
+  <si>
+    <t>Sheet Category</t>
+  </si>
+  <si>
+    <t>Document Domain</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Technical Workbench Logs</t>
+  </si>
+  <si>
+    <t>PROJECT ERROR LOG DATABASE</t>
+  </si>
+  <si>
+    <t>Contains error codes, stream configurations, developers, and resolution steps.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dd\,\ yyyy"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-  </numFmts>
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -434,6 +543,11 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="3">
@@ -490,7 +604,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -531,15 +645,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="2"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -555,17 +660,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1" indent="3"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="10">
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0">
@@ -585,22 +694,6 @@
     </dxf>
     <dxf>
       <alignment wrapText="1"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="dd/mm/yyyy"/>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="thin">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom/>
-      </border>
     </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -767,17 +860,20 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8218E10-27D8-4199-A310-EF2F29294419}" name="Table1" displayName="Table1" ref="A1:I27" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9">
-  <autoFilter ref="A1:I27" xr:uid="{C8218E10-27D8-4199-A310-EF2F29294419}"/>
-  <tableColumns count="9">
-    <tableColumn id="1" xr3:uid="{4D214576-3A2A-4EA3-942A-5AE0C4D921C8}" name="Developer" dataDxfId="8"/>
-    <tableColumn id="5" xr3:uid="{40FC3A1A-F761-4C4C-A092-BFC0BB2013D7}" name="Stream Name-Setup Number" dataDxfId="7"/>
-    <tableColumn id="4" xr3:uid="{EFCB3567-1A5D-4AFB-8DC4-59FFC628D30D}" name="WorkBench Error Code" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{7BC6EB0D-5B6A-40D8-9197-2C776DF2E3DE}" name="Error Message" dataDxfId="5"/>
-    <tableColumn id="6" xr3:uid="{AF06E84F-EC79-4156-A4F7-D8B35E587215}" name="Category (Transformation/Profile/Other)" dataDxfId="4"/>
-    <tableColumn id="7" xr3:uid="{8164D0A7-56C6-4CF7-B6C8-C446F24CC5FA}" name="Knowledge Source" dataDxfId="3"/>
-    <tableColumn id="8" xr3:uid="{017257B6-2629-45C5-8F8A-C4B26B3B906C}" name="Date" dataDxfId="2"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8218E10-27D8-4199-A310-EF2F29294419}" name="Table1" displayName="Table1" ref="A1:H36" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
+  <autoFilter ref="A1:H36" xr:uid="{C8218E10-27D8-4199-A310-EF2F29294419}"/>
+  <tableColumns count="8">
+    <tableColumn id="1" xr3:uid="{4D214576-3A2A-4EA3-942A-5AE0C4D921C8}" name="Developer" dataDxfId="7"/>
+    <tableColumn id="5" xr3:uid="{40FC3A1A-F761-4C4C-A092-BFC0BB2013D7}" name="Stream Name-Setup Number" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{EFCB3567-1A5D-4AFB-8DC4-59FFC628D30D}" name="WorkBench Error Code" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{7BC6EB0D-5B6A-40D8-9197-2C776DF2E3DE}" name="Error Message" dataDxfId="4"/>
+    <tableColumn id="6" xr3:uid="{AF06E84F-EC79-4156-A4F7-D8B35E587215}" name="Category (Transformation/Profile/Other)" dataDxfId="3"/>
+    <tableColumn id="7" xr3:uid="{8164D0A7-56C6-4CF7-B6C8-C446F24CC5FA}" name="Knowledge Source" dataDxfId="2"/>
     <tableColumn id="9" xr3:uid="{9343B300-6B21-4EDE-A0BF-54FD39302602}" name="Jira/Email detail" dataDxfId="1"/>
     <tableColumn id="3" xr3:uid="{5E52460C-1D9C-4EBB-9277-AFA43E689BA1}" name="Resolution Steps" dataDxfId="0"/>
   </tableColumns>
@@ -1101,18 +1197,55 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3775EE33-B872-4E10-90AB-177DCEAAC69A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="72" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>113</v>
+      </c>
+      <c r="C1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultRowHeight="65.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="40.5703125" style="2" customWidth="1"/>
     <col min="3" max="3" width="16.140625" style="2" customWidth="1"/>
     <col min="4" max="4" width="77" style="8" customWidth="1"/>
-    <col min="5" max="5" width="23.28515625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="23.85546875" style="21" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" style="17" customWidth="1"/>
-    <col min="8" max="8" width="29.42578125" customWidth="1"/>
+    <col min="5" max="5" width="32.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="23.85546875" style="18" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" style="14" customWidth="1"/>
+    <col min="8" max="8" width="41.7109375" customWidth="1"/>
     <col min="9" max="9" width="95.28515625" customWidth="1"/>
     <col min="10" max="10" width="110.5703125" style="12" customWidth="1"/>
   </cols>
@@ -1133,636 +1266,811 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="17" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="14" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="9" t="s">
         <v>7</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>8</v>
       </c>
       <c r="J1"/>
     </row>
     <row r="2" spans="1:10" ht="65.25" customHeight="1">
       <c r="A2" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3"/>
+      <c r="D2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="6" t="s">
+      <c r="E2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F2" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="G2" s="2"/>
+      <c r="H2" s="10" t="s">
         <v>13</v>
-      </c>
-      <c r="F2" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" s="15"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="10" t="s">
-        <v>15</v>
       </c>
       <c r="J2"/>
     </row>
     <row r="3" spans="1:10" ht="102" customHeight="1">
       <c r="A3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="C3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F3" s="15"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="10" t="s">
         <v>16</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="18"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="10" t="s">
-        <v>18</v>
       </c>
       <c r="J3"/>
     </row>
     <row r="4" spans="1:10" ht="65.25" customHeight="1">
       <c r="A4" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="F4" s="15"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="15"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="10" t="s">
-        <v>22</v>
       </c>
       <c r="J4"/>
     </row>
     <row r="5" spans="1:10" ht="112.5" customHeight="1">
       <c r="A5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="D5" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F5" s="15"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="10" t="s">
         <v>25</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="15"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="10" t="s">
-        <v>27</v>
       </c>
       <c r="J5"/>
     </row>
     <row r="6" spans="1:10" ht="141" customHeight="1">
       <c r="A6" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="D6" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="E6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" s="16"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="11" t="s">
         <v>30</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F6" s="19"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="11" t="s">
-        <v>32</v>
       </c>
       <c r="J6"/>
     </row>
     <row r="7" spans="1:10" ht="96.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D7" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F7" s="16"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="11" t="s">
         <v>33</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F7" s="19"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="11" t="s">
-        <v>34</v>
       </c>
       <c r="J7"/>
     </row>
     <row r="8" spans="1:10" ht="65.25" customHeight="1">
       <c r="A8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="C8" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="7" t="s">
+      <c r="E8" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F8" s="16"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="11" t="s">
         <v>37</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F8" s="19"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="11" t="s">
-        <v>38</v>
       </c>
       <c r="J8"/>
     </row>
     <row r="9" spans="1:10" ht="65.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="E9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F9" s="16"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="11" t="s">
         <v>40</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F9" s="19"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="11" t="s">
-        <v>41</v>
       </c>
       <c r="J9"/>
     </row>
     <row r="10" spans="1:10" ht="65.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B10" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F10" s="16"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="11" t="s">
         <v>43</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="16"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="11" t="s">
-        <v>44</v>
       </c>
       <c r="J10"/>
     </row>
     <row r="11" spans="1:10" ht="65.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="C11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="D11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="E11" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="F11" s="16"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="11" t="s">
         <v>48</v>
-      </c>
-      <c r="F11" s="19"/>
-      <c r="G11" s="16"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="11" t="s">
-        <v>49</v>
       </c>
       <c r="J11"/>
     </row>
     <row r="12" spans="1:10" ht="65.25" customHeight="1">
       <c r="A12" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D12" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F12" s="16"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="11" t="s">
         <v>50</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F12" s="19"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="11" t="s">
-        <v>51</v>
       </c>
       <c r="J12"/>
     </row>
     <row r="13" spans="1:10" ht="65.25" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D13" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F13" s="16"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="11" t="s">
         <v>52</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="16"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="11" t="s">
-        <v>53</v>
       </c>
       <c r="J13"/>
     </row>
     <row r="14" spans="1:10" ht="65.25" customHeight="1">
       <c r="A14" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="11" t="s">
         <v>54</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="16"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="11" t="s">
-        <v>55</v>
       </c>
       <c r="J14"/>
     </row>
     <row r="15" spans="1:10" ht="65.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E15" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="16"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="11" t="s">
         <v>56</v>
-      </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="16"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="11" t="s">
-        <v>57</v>
       </c>
       <c r="J15"/>
     </row>
     <row r="16" spans="1:10" ht="65.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D16" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F16" s="16"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="11" t="s">
         <v>58</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F16" s="19"/>
-      <c r="G16" s="16"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="11" t="s">
-        <v>59</v>
       </c>
       <c r="J16"/>
     </row>
     <row r="17" spans="1:10" ht="65.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D17" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F17" s="16"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="11" t="s">
         <v>60</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F17" s="19"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="11" t="s">
-        <v>61</v>
       </c>
       <c r="J17"/>
     </row>
     <row r="18" spans="1:10" ht="65.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D18" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F18" s="16"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="11" t="s">
         <v>62</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F18" s="19"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="11" t="s">
-        <v>63</v>
       </c>
       <c r="J18"/>
     </row>
     <row r="19" spans="1:10" ht="65.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D19" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="11" t="s">
         <v>64</v>
-      </c>
-      <c r="E19" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="16"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="11" t="s">
-        <v>65</v>
       </c>
       <c r="J19"/>
     </row>
     <row r="20" spans="1:10" ht="65.25" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D20" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F20" s="16"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="11" t="s">
         <v>66</v>
-      </c>
-      <c r="E20" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F20" s="19"/>
-      <c r="G20" s="16"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="11" t="s">
-        <v>67</v>
       </c>
       <c r="J20"/>
     </row>
     <row r="21" spans="1:10" ht="65.25" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="D21" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F21" s="16"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="11" t="s">
         <v>68</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F21" s="19"/>
-      <c r="G21" s="16"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="11" t="s">
-        <v>69</v>
       </c>
       <c r="J21"/>
     </row>
     <row r="22" spans="1:10" ht="65.25" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D22" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F22" s="16"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="11" t="s">
         <v>70</v>
-      </c>
-      <c r="E22" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F22" s="19"/>
-      <c r="G22" s="16"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="11" t="s">
-        <v>71</v>
       </c>
       <c r="J22"/>
     </row>
     <row r="23" spans="1:10" ht="65.25" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B23" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D23" s="13" t="s">
         <v>72</v>
       </c>
-      <c r="C23" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="13" t="s">
+      <c r="E23" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F23" s="16"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="11" t="s">
         <v>73</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F23" s="19"/>
-      <c r="G23" s="16"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="11" t="s">
-        <v>74</v>
       </c>
       <c r="J23"/>
     </row>
     <row r="24" spans="1:10" ht="92.25" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B24" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C24" s="4" t="s">
         <v>75</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="D24" s="13" t="s">
         <v>76</v>
       </c>
-      <c r="D24" s="13" t="s">
+      <c r="E24" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="F24" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="19" t="s">
+      <c r="G24" s="2"/>
+      <c r="H24" s="11" t="s">
         <v>79</v>
-      </c>
-      <c r="G24" s="16">
-        <v>46191</v>
-      </c>
-      <c r="H24" s="2"/>
-      <c r="I24" s="11" t="s">
-        <v>80</v>
       </c>
       <c r="J24"/>
     </row>
     <row r="25" spans="1:10" ht="65.25" customHeight="1">
       <c r="A25" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="C25" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="C25" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D25" s="13" t="s">
+      <c r="E25" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="F25" s="16"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="11" t="s">
         <v>84</v>
       </c>
-      <c r="F25" s="19"/>
-      <c r="G25" s="22"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="11" t="s">
-        <v>85</v>
-      </c>
+      <c r="I25" s="12"/>
+      <c r="J25"/>
     </row>
     <row r="26" spans="1:10" ht="65.25" customHeight="1">
       <c r="A26" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B26" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="C26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="C26" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="D26" s="13" t="s">
+      <c r="E26" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F26" s="16"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>84</v>
-      </c>
-      <c r="F26" s="19"/>
-      <c r="G26" s="22">
-        <v>46203</v>
-      </c>
-      <c r="H26" s="2"/>
-      <c r="I26" s="11" t="s">
+      <c r="I26" s="12"/>
+      <c r="J26"/>
+    </row>
+    <row r="27" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A27" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="27" spans="1:10" ht="65.25" customHeight="1">
-      <c r="A27" s="4"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="4"/>
-      <c r="F27" s="19"/>
-      <c r="G27" s="22"/>
-      <c r="H27" s="23"/>
-      <c r="I27" s="11"/>
+      <c r="C27" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F27" s="16"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="I27" s="12"/>
+      <c r="J27"/>
+    </row>
+    <row r="28" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A28" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="16"/>
+      <c r="H28" s="19" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A29" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="16"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A30" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F30" s="16"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A31" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F31" s="16"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="11" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A32" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D32" s="20" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F32" s="16"/>
+      <c r="H32" s="11" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="65.25" customHeight="1">
+      <c r="A33" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="D33" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="E33" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F33" s="16"/>
+      <c r="H33" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="65.25" customHeight="1">
+      <c r="A34" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E34" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="F34" s="16"/>
+      <c r="G34" s="2"/>
+      <c r="H34" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="65.25" customHeight="1">
+      <c r="A35" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="E35" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="F35" s="16"/>
+      <c r="G35" s="2"/>
+      <c r="H35" s="11" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="65.25" customHeight="1">
+      <c r="A36" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="D36" s="13" t="s">
+        <v>111</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="F36" s="16"/>
+      <c r="H36" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/source_docs/Ithaka-Portico-KnowledgeBase.xlsx
+++ b/source_docs/Ithaka-Portico-KnowledgeBase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://innodata-my.sharepoint.com/personal/vff_innodata_com/Documents/Shared with Everyone/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="450" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E5890746-5E04-45E4-BA60-06D5E034FCD7}"/>
+  <xr:revisionPtr revIDLastSave="575" documentId="11_0B1D56BE9CDCCE836B02CE7A5FB0D4A9BBFD1C62" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{98327407-02CE-4314-8920-07B308AAB8D9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="00_DOMAINS_AND_METADATA" sheetId="2" r:id="rId1"/>
@@ -36,8 +36,48 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="143">
+  <si>
+    <t>Sheet Category</t>
+  </si>
+  <si>
+    <t>Document Domain</t>
+  </si>
+  <si>
+    <t>Scope</t>
+  </si>
+  <si>
+    <t>Technical Workbench Logs</t>
+  </si>
+  <si>
+    <t>PROJECT ERROR LOG DATABASE</t>
+  </si>
+  <si>
+    <t>Contains error codes, stream configurations, developers, and resolution steps.</t>
+  </si>
   <si>
     <t>Developer</t>
   </si>
@@ -507,22 +547,94 @@
 Generated file EMERALD E-Books/978-1-59311-357-5/xml/conprep_generated/tms2gvmxdb1 well-formed but not valid.</t>
   </si>
   <si>
-    <t>Sheet Category</t>
-  </si>
-  <si>
-    <t>Document Domain</t>
-  </si>
-  <si>
-    <t>Scope</t>
-  </si>
-  <si>
-    <t>Technical Workbench Logs</t>
-  </si>
-  <si>
-    <t>PROJECT ERROR LOG DATABASE</t>
-  </si>
-  <si>
-    <t>Contains error codes, stream configurations, developers, and resolution steps.</t>
+    <t>- Correct the sequence of element in script.
+- Updated template book-meta.</t>
+  </si>
+  <si>
+    <t>MARKALLEN Atypon E-Journals BL-SETUP-25204</t>
+  </si>
+  <si>
+    <t>C804</t>
+  </si>
+  <si>
+    <t>C804 : CU 1 (Category: Processing) Step : PorticoWorkflow_4_3_AssignContentSetName
+No Curated DMD found for CU (CU 1)</t>
+  </si>
+  <si>
+    <t>- CU Token of XML, PDF and Image files are not correct to identified by the current rule 'InterpretPackagingRuleSet'
+- Resolution: We created the new IP rules after that now files are correct identified.</t>
+  </si>
+  <si>
+    <t>- Correct the sequence of element in script.
+- Updated template licence.</t>
+  </si>
+  <si>
+    <t>C500 : SU 3 (Category: Processing) Step : PorticoWorkflow_4_3_TransformFiles
+Failed to transform the supplied file '/pcontent/ongoing/journal_content/INGEST_MASTER/_eBooks/EMERALD/Fetched/SILVERCHAIR-BOOKS/NEW/Books/978-0-7277-6094-4_2025-11-13.zip/9780727760944.xml' '/pcontent/ongoing/journal_content/INGEST_MASTER/_eBooks/EMERALD/Fetched/SILVERCHAIR-BOOKS/NEW/Books/978-0-7277-6094-4_2025-11-13.zip/grasp.60944.001.xml'</t>
+  </si>
+  <si>
+    <t>- CU Token of XML, Review PDF files are not correct to identified by the current rule 'InterpretPackagingRuleSet'
+- Resolution: We have updated exsiting rule to identify the file.</t>
+  </si>
+  <si>
+    <t>C448 (Category: Configuration) Step : PorticoWorkflow_4_3_CheckForCompleteness
+Orphan File /pcontent/ongoing/journal_content/INGEST_MASTER/_eBooks/EMERALD/Fetched/SILVERCHAIR-BOOKS/NEW/Books/978-0-72776-704-2_2025-10-29_20251030034603.zip/cmsb_67042_0969_fa1.png: not fully unit identified.
+Messages Content:
+Check file naming and Profile rules</t>
+  </si>
+  <si>
+    <t>- New pattern of image files are porvided in the ZIP.
+- Resolution: We have updated the IP rule to move these kind of file in respective CU.</t>
+  </si>
+  <si>
+    <t>C522</t>
+  </si>
+  <si>
+    <t>C522 (Category: Processing) Step : PorticoWorkflow_4_3_CheckForCompleteness
+For CU 1, Expected Fu types Check Failed. For additional info check below info messages.
+Messages Content:
+Check expected FU types rule.</t>
+  </si>
+  <si>
+    <t>- Book PDF file is not as per ExpectedFuTypes in Profile.
+- Resolution: Created New EFT rule to solve the problem</t>
+  </si>
+  <si>
+    <t>ILLINOIS Silverchair E-Journals-SETUP-24500</t>
+  </si>
+  <si>
+    <t>C510 : SU 5 (Category: Processing) Step : PorticoWorkflow_4_3_ResolveFileReferences
+File etmv69i2.zip/401696/etm21567417.69.2.03figure1.png not referenced in the generated(target) lead MD file etm/401696/145yamin-xml/conprep_generated/tms3xq38n3h</t>
+  </si>
+  <si>
+    <t>- These types of error are fixed by Profile in FileReferenceCheckExclusionSet.</t>
+  </si>
+  <si>
+    <t>Upstream Dependencies</t>
+  </si>
+  <si>
+    <t>Downstream Impacted Modules</t>
+  </si>
+  <si>
+    <t>XML Schemas (XSD) | External DTDs: | Configuration Files</t>
+  </si>
+  <si>
+    <t>XSLT Stylesheets | Conprep Workbench</t>
+  </si>
+  <si>
+    <t>Failed Data Pipelines | Mismatched URLs</t>
+  </si>
+  <si>
+    <t>Submission Profile | Registries | Downstream APIs</t>
+  </si>
+  <si>
+    <t>Publisher Website Access Issue</t>
+  </si>
+  <si>
+    <t>Ithaka CMI</t>
+  </si>
+  <si>
+    <t>Submission Profile | Registries | Downstream APIs | XSLT Scripts</t>
   </si>
 </sst>
 </file>
@@ -674,22 +786,24 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="10">
+  <dxfs count="12">
+    <dxf>
+      <alignment horizontal="general" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment wrapText="1"/>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color rgb="FF000000"/>
         </left>
-        <right style="thin">
-          <color rgb="FF000000"/>
-        </right>
+        <right/>
         <top style="thin">
           <color rgb="FF000000"/>
         </top>
         <bottom/>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -860,22 +974,20 @@
 </styleSheet>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8218E10-27D8-4199-A310-EF2F29294419}" name="Table1" displayName="Table1" ref="A1:H36" totalsRowShown="0" headerRowDxfId="9" dataDxfId="8">
-  <autoFilter ref="A1:H36" xr:uid="{C8218E10-27D8-4199-A310-EF2F29294419}"/>
-  <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{4D214576-3A2A-4EA3-942A-5AE0C4D921C8}" name="Developer" dataDxfId="7"/>
-    <tableColumn id="5" xr3:uid="{40FC3A1A-F761-4C4C-A092-BFC0BB2013D7}" name="Stream Name-Setup Number" dataDxfId="6"/>
-    <tableColumn id="4" xr3:uid="{EFCB3567-1A5D-4AFB-8DC4-59FFC628D30D}" name="WorkBench Error Code" dataDxfId="5"/>
-    <tableColumn id="2" xr3:uid="{7BC6EB0D-5B6A-40D8-9197-2C776DF2E3DE}" name="Error Message" dataDxfId="4"/>
-    <tableColumn id="6" xr3:uid="{AF06E84F-EC79-4156-A4F7-D8B35E587215}" name="Category (Transformation/Profile/Other)" dataDxfId="3"/>
-    <tableColumn id="7" xr3:uid="{8164D0A7-56C6-4CF7-B6C8-C446F24CC5FA}" name="Knowledge Source" dataDxfId="2"/>
-    <tableColumn id="9" xr3:uid="{9343B300-6B21-4EDE-A0BF-54FD39302602}" name="Jira/Email detail" dataDxfId="1"/>
-    <tableColumn id="3" xr3:uid="{5E52460C-1D9C-4EBB-9277-AFA43E689BA1}" name="Resolution Steps" dataDxfId="0"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{C8218E10-27D8-4199-A310-EF2F29294419}" name="Table1" displayName="Table1" ref="A1:J43" totalsRowShown="0" headerRowDxfId="11" dataDxfId="10">
+  <autoFilter ref="A1:J43" xr:uid="{C8218E10-27D8-4199-A310-EF2F29294419}"/>
+  <tableColumns count="10">
+    <tableColumn id="1" xr3:uid="{4D214576-3A2A-4EA3-942A-5AE0C4D921C8}" name="Developer" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{40FC3A1A-F761-4C4C-A092-BFC0BB2013D7}" name="Stream Name-Setup Number" dataDxfId="8"/>
+    <tableColumn id="4" xr3:uid="{EFCB3567-1A5D-4AFB-8DC4-59FFC628D30D}" name="WorkBench Error Code" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{7BC6EB0D-5B6A-40D8-9197-2C776DF2E3DE}" name="Error Message" dataDxfId="6"/>
+    <tableColumn id="6" xr3:uid="{AF06E84F-EC79-4156-A4F7-D8B35E587215}" name="Category (Transformation/Profile/Other)" dataDxfId="5"/>
+    <tableColumn id="7" xr3:uid="{8164D0A7-56C6-4CF7-B6C8-C446F24CC5FA}" name="Knowledge Source" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{9343B300-6B21-4EDE-A0BF-54FD39302602}" name="Jira/Email detail" dataDxfId="3"/>
+    <tableColumn id="3" xr3:uid="{5E52460C-1D9C-4EBB-9277-AFA43E689BA1}" name="Resolution Steps" dataDxfId="2"/>
+    <tableColumn id="8" xr3:uid="{C9DCE501-E325-47F5-BBA0-503FB4B02FC3}" name="Upstream Dependencies" dataDxfId="0"/>
+    <tableColumn id="10" xr3:uid="{C666B494-B8F3-4E8B-845C-EF62DDCACF45}" name="Downstream Impacted Modules" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1201,31 +1313,31 @@
   <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="28.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="72" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="29.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="69.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>113</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>114</v>
+        <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>3</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
-        <v>117</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1235,842 +1347,1218 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr defaultRowHeight="65.25" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20.140625" style="2" customWidth="1"/>
     <col min="2" max="2" width="40.5703125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="16.140625" style="2" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" style="2" customWidth="1"/>
     <col min="4" max="4" width="77" style="8" customWidth="1"/>
     <col min="5" max="5" width="32.140625" style="2" customWidth="1"/>
     <col min="6" max="6" width="23.85546875" style="18" customWidth="1"/>
     <col min="7" max="7" width="13.7109375" style="14" customWidth="1"/>
     <col min="8" max="8" width="41.7109375" customWidth="1"/>
-    <col min="9" max="9" width="95.28515625" customWidth="1"/>
-    <col min="10" max="10" width="110.5703125" style="12" customWidth="1"/>
+    <col min="9" max="9" width="30.140625" style="2" customWidth="1"/>
+    <col min="10" max="10" width="34.140625" style="12" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="27.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F1" s="17" t="s">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="J1"/>
-    </row>
-    <row r="2" spans="1:10" ht="65.25" customHeight="1">
+        <v>13</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="122.25" customHeight="1">
       <c r="A2" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="6" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F2" s="15" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2"/>
       <c r="H2" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="J2"/>
+        <v>19</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="3" spans="1:10" ht="102" customHeight="1">
       <c r="A3" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F3" s="15"/>
       <c r="G3" s="2"/>
       <c r="H3" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="J3"/>
-    </row>
-    <row r="4" spans="1:10" ht="65.25" customHeight="1">
+        <v>22</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="125.25" customHeight="1">
       <c r="A4" s="3" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F4" s="15"/>
       <c r="G4" s="2"/>
       <c r="H4" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4"/>
+        <v>26</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="5" spans="1:10" ht="112.5" customHeight="1">
       <c r="A5" s="3" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F5" s="15"/>
       <c r="G5" s="2"/>
       <c r="H5" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="J5"/>
+        <v>31</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="6" spans="1:10" ht="141" customHeight="1">
       <c r="A6" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F6" s="16"/>
       <c r="G6" s="2"/>
       <c r="H6" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6"/>
+        <v>36</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="7" spans="1:10" ht="96.75" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F7" s="16"/>
       <c r="G7" s="2"/>
       <c r="H7" s="11" t="s">
-        <v>33</v>
-      </c>
-      <c r="J7"/>
+        <v>39</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="8" spans="1:10" ht="65.25" customHeight="1">
       <c r="A8" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F8" s="16"/>
       <c r="G8" s="2"/>
       <c r="H8" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="J8"/>
+        <v>43</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="9" spans="1:10" ht="65.25" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F9" s="16"/>
       <c r="G9" s="2"/>
       <c r="H9" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="J9"/>
+        <v>46</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="10" spans="1:10" ht="65.25" customHeight="1">
       <c r="A10" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F10" s="16"/>
       <c r="G10" s="2"/>
       <c r="H10" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="J10"/>
+        <v>49</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="11" spans="1:10" ht="65.25" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="F11" s="16"/>
       <c r="G11" s="2"/>
       <c r="H11" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="J11"/>
+        <v>54</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="12" spans="1:10" ht="65.25" customHeight="1">
       <c r="A12" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B12" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="D12" s="7" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F12" s="16"/>
       <c r="G12" s="2"/>
       <c r="H12" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="J12"/>
+        <v>56</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="13" spans="1:10" ht="65.25" customHeight="1">
       <c r="A13" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="D13" s="7" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F13" s="16"/>
       <c r="G13" s="2"/>
       <c r="H13" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="J13"/>
+        <v>58</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="14" spans="1:10" ht="65.25" customHeight="1">
       <c r="A14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B14" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>28</v>
-      </c>
       <c r="D14" s="7" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F14" s="16"/>
       <c r="G14" s="2"/>
       <c r="H14" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="J14"/>
+        <v>60</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="15" spans="1:10" ht="65.25" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="F15" s="16"/>
       <c r="G15" s="2"/>
       <c r="H15" s="11" t="s">
-        <v>56</v>
-      </c>
-      <c r="J15"/>
+        <v>62</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="16" spans="1:10" ht="65.25" customHeight="1">
       <c r="A16" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F16" s="16"/>
       <c r="G16" s="2"/>
       <c r="H16" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="J16"/>
+        <v>64</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="17" spans="1:10" ht="65.25" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F17" s="16"/>
       <c r="G17" s="2"/>
       <c r="H17" s="11" t="s">
-        <v>60</v>
-      </c>
-      <c r="J17"/>
+        <v>66</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="18" spans="1:10" ht="65.25" customHeight="1">
       <c r="A18" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F18" s="16"/>
       <c r="G18" s="2"/>
       <c r="H18" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="J18"/>
+        <v>68</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="19" spans="1:10" ht="65.25" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D19" s="7" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F19" s="16"/>
       <c r="G19" s="2"/>
       <c r="H19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="J19"/>
+        <v>70</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="20" spans="1:10" ht="65.25" customHeight="1">
       <c r="A20" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D20" s="7" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F20" s="16"/>
       <c r="G20" s="2"/>
       <c r="H20" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="J20"/>
+        <v>72</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="21" spans="1:10" ht="65.25" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F21" s="16"/>
       <c r="G21" s="2"/>
       <c r="H21" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="J21"/>
+        <v>74</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="22" spans="1:10" ht="65.25" customHeight="1">
       <c r="A22" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F22" s="16"/>
       <c r="G22" s="2"/>
       <c r="H22" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="J22"/>
+        <v>76</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="23" spans="1:10" ht="65.25" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F23" s="16"/>
       <c r="G23" s="2"/>
       <c r="H23" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="J23"/>
+        <v>79</v>
+      </c>
+      <c r="J23" s="2"/>
     </row>
     <row r="24" spans="1:10" ht="92.25" customHeight="1">
       <c r="A24" s="4" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D24" s="13" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G24" s="2"/>
       <c r="H24" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="J24"/>
+        <v>85</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
     <row r="25" spans="1:10" ht="65.25" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D25" s="13" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F25" s="16"/>
       <c r="G25" s="2"/>
       <c r="H25" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="I25" s="12"/>
-      <c r="J25"/>
+        <v>90</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="26" spans="1:10" ht="65.25" customHeight="1">
       <c r="A26" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D26" s="13" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F26" s="16"/>
       <c r="G26" s="2"/>
       <c r="H26" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="I26" s="12"/>
-      <c r="J26"/>
+        <v>94</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>137</v>
+      </c>
     </row>
     <row r="27" spans="1:10" ht="65.25" customHeight="1">
       <c r="A27" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B27" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="E27" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="F27" s="16"/>
       <c r="G27" s="2"/>
       <c r="H27" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="I27" s="12"/>
-      <c r="J27"/>
+        <v>98</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
     <row r="28" spans="1:10" ht="65.25" customHeight="1">
       <c r="A28" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F28" s="16"/>
       <c r="H28" s="19" t="s">
-        <v>95</v>
+        <v>101</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:10" ht="65.25" customHeight="1">
       <c r="A29" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B29" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>89</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="D29" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>83</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="2"/>
       <c r="H29" s="11" t="s">
-        <v>97</v>
+        <v>103</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="30" spans="1:10" ht="65.25" customHeight="1">
       <c r="A30" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D30" s="7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F30" s="16"/>
       <c r="G30" s="2"/>
       <c r="H30" s="11" t="s">
-        <v>100</v>
+        <v>106</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:10" ht="65.25" customHeight="1">
       <c r="A31" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F31" s="16"/>
       <c r="G31" s="2"/>
       <c r="H31" s="11" t="s">
-        <v>101</v>
+        <v>107</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="65.25" customHeight="1">
       <c r="A32" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D32" s="20" t="s">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F32" s="16"/>
       <c r="H32" s="11" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="65.25" customHeight="1">
+        <v>109</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J32" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" ht="65.25" customHeight="1">
       <c r="A33" s="4" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>93</v>
+        <v>99</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="D33" s="13" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F33" s="16"/>
       <c r="H33" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="65.25" customHeight="1">
+        <v>111</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J33" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" ht="65.25" customHeight="1">
       <c r="A34" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D34" s="7" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E34" s="21" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F34" s="16"/>
       <c r="G34" s="2"/>
       <c r="H34" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="65.25" customHeight="1">
+        <v>114</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J34" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" ht="65.25" customHeight="1">
       <c r="A35" s="4" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D35" s="7" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F35" s="16"/>
       <c r="G35" s="2"/>
       <c r="H35" s="11" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="65.25" customHeight="1">
+        <v>116</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J35" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10" ht="65.25" customHeight="1">
       <c r="A36" s="4" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="F36" s="16"/>
-      <c r="H36" s="11"/>
+      <c r="H36" s="11" t="s">
+        <v>118</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J36" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A37" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D37" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F37" s="16"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="11" t="s">
+        <v>122</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J37" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A38" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F38" s="16"/>
+      <c r="H38" s="11" t="s">
+        <v>123</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J38" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A39" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F39" s="16"/>
+      <c r="H39" s="11" t="e" cm="1">
+        <f t="array" ref="H39">- Add new elements in unhandled template.
+- Created template with logic as per publisher.</f>
+        <v>#NAME?</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="J39" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A40" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D40" s="13" t="s">
+        <v>121</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F40" s="16"/>
+      <c r="G40" s="2"/>
+      <c r="H40" s="11" t="s">
+        <v>125</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J40" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A41" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="D41" s="13" t="s">
+        <v>126</v>
+      </c>
+      <c r="E41" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F41" s="16"/>
+      <c r="H41" s="11" t="s">
+        <v>127</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A42" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D42" s="13" t="s">
+        <v>129</v>
+      </c>
+      <c r="E42" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F42" s="16"/>
+      <c r="H42" s="11" t="s">
+        <v>130</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J42" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10" ht="65.25" customHeight="1">
+      <c r="A43" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D43" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F43" s="16"/>
+      <c r="H43" s="11" t="s">
+        <v>133</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="J43" s="2" t="s">
+        <v>142</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
